--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18473,6 +18473,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B788" t="n">
+        <v>22500</v>
+      </c>
+      <c r="C788" t="n">
+        <v>1.38499999046326</v>
+      </c>
+      <c r="D788" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="E788" t="n">
+        <v>1.38499999046326</v>
+      </c>
+      <c r="F788" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G788" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18496,6 +18496,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B789" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C789" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D789" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E789" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F789" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G789" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18519,6 +18519,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B790" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C790" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D790" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E790" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F790" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G790" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18542,6 +18542,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B791" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C791" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D791" t="n">
+        <v>1.43499994277954</v>
+      </c>
+      <c r="E791" t="n">
+        <v>1.43499994277954</v>
+      </c>
+      <c r="F791" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18383,22 +18383,22 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B784" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C784" t="n">
-        <v>1.48000001907349</v>
+        <v>1.47500002384186</v>
       </c>
       <c r="D784" t="n">
-        <v>1.44500005245209</v>
+        <v>1.47500002384186</v>
       </c>
       <c r="E784" t="n">
         <v>1.47500002384186</v>
       </c>
       <c r="F784" t="n">
-        <v>1.44500005245209</v>
+        <v>1.47500002384186</v>
       </c>
       <c r="G784" t="s">
         <v>7</v>
@@ -18406,22 +18406,22 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B785" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="C785" t="n">
-        <v>1.45000004768372</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="D785" t="n">
-        <v>1.41999995708466</v>
+        <v>1.44500005245209</v>
       </c>
       <c r="E785" t="n">
-        <v>1.41999995708466</v>
+        <v>1.47500002384186</v>
       </c>
       <c r="F785" t="n">
-        <v>1.45000004768372</v>
+        <v>1.44500005245209</v>
       </c>
       <c r="G785" t="s">
         <v>7</v>
@@ -18429,22 +18429,22 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B786" t="n">
-        <v>19500</v>
+        <v>3000</v>
       </c>
       <c r="C786" t="n">
-        <v>1.45500004291534</v>
+        <v>1.45000004768372</v>
       </c>
       <c r="D786" t="n">
-        <v>1.43499994277954</v>
+        <v>1.41999995708466</v>
       </c>
       <c r="E786" t="n">
-        <v>1.45500004291534</v>
+        <v>1.41999995708466</v>
       </c>
       <c r="F786" t="n">
-        <v>1.43499994277954</v>
+        <v>1.45000004768372</v>
       </c>
       <c r="G786" t="s">
         <v>7</v>
@@ -18452,22 +18452,22 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B787" t="n">
-        <v>4500</v>
+        <v>19500</v>
       </c>
       <c r="C787" t="n">
-        <v>1.4099999666214</v>
+        <v>1.45500004291534</v>
       </c>
       <c r="D787" t="n">
-        <v>1.40499997138977</v>
+        <v>1.43499994277954</v>
       </c>
       <c r="E787" t="n">
-        <v>1.4099999666214</v>
+        <v>1.45500004291534</v>
       </c>
       <c r="F787" t="n">
-        <v>1.4099999666214</v>
+        <v>1.43499994277954</v>
       </c>
       <c r="G787" t="s">
         <v>7</v>
@@ -18475,22 +18475,22 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B788" t="n">
-        <v>22500</v>
+        <v>4500</v>
       </c>
       <c r="C788" t="n">
-        <v>1.38499999046326</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="D788" t="n">
-        <v>1.33500003814697</v>
+        <v>1.40499997138977</v>
       </c>
       <c r="E788" t="n">
-        <v>1.38499999046326</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="F788" t="n">
-        <v>1.375</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="G788" t="s">
         <v>7</v>
@@ -18498,22 +18498,22 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B789" t="n">
-        <v>15000</v>
+        <v>22500</v>
       </c>
       <c r="C789" t="n">
+        <v>1.38499999046326</v>
+      </c>
+      <c r="D789" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="E789" t="n">
+        <v>1.38499999046326</v>
+      </c>
+      <c r="F789" t="n">
         <v>1.375</v>
-      </c>
-      <c r="D789" t="n">
-        <v>1.3400000333786</v>
-      </c>
-      <c r="E789" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="F789" t="n">
-        <v>1.35000002384186</v>
       </c>
       <c r="G789" t="s">
         <v>7</v>
@@ -18521,22 +18521,22 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B790" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="C790" t="n">
-        <v>1.4099999666214</v>
+        <v>1.375</v>
       </c>
       <c r="D790" t="n">
-        <v>1.37999999523163</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="E790" t="n">
-        <v>1.37999999523163</v>
+        <v>1.375</v>
       </c>
       <c r="F790" t="n">
-        <v>1.4099999666214</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="G790" t="s">
         <v>7</v>
@@ -18544,24 +18544,47 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B791" t="n">
         <v>7500</v>
       </c>
       <c r="C791" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D791" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E791" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F791" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B792" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C792" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D792" t="n">
         <v>1.44000005722046</v>
       </c>
-      <c r="D791" t="n">
-        <v>1.43499994277954</v>
-      </c>
-      <c r="E791" t="n">
-        <v>1.43499994277954</v>
-      </c>
-      <c r="F791" t="n">
+      <c r="E792" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F792" t="n">
         <v>1.44000005722046</v>
       </c>
-      <c r="G791" t="s">
+      <c r="G792" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -21019,6 +21019,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B795" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C795" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D795" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E795" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F795" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="G795" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="H795" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -21045,6 +21045,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B796" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C796" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="D796" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E796" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F796" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="G796" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="H796" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -21071,6 +21071,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B797" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C797" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="D797" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E797" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F797" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G797" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="H797" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -21097,6 +21097,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B798" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C798" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="D798" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E798" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F798" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G798" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="H798" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -21175,6 +21175,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B801" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C801" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D801" t="n">
+        <v>1.40499997138977</v>
+      </c>
+      <c r="E801" t="n">
+        <v>1.40499997138977</v>
+      </c>
+      <c r="F801" t="n">
+        <v>1.41499996185303</v>
+      </c>
+      <c r="G801" t="n">
+        <v>1.41499996185303</v>
+      </c>
+      <c r="H801" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18857,8 +18857,31 @@
       <c r="E804" t="n">
         <v>1.49500000476837</v>
       </c>
-      <c r="F804"/>
+      <c r="F804" t="n">
+        <v>1.47500002384186</v>
+      </c>
       <c r="G804" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C805" t="n">
+        <v>1.51499998569489</v>
+      </c>
+      <c r="D805" t="n">
+        <v>1.47500002384186</v>
+      </c>
+      <c r="E805" t="n">
+        <v>1.49500000476837</v>
+      </c>
+      <c r="F805"/>
+      <c r="G805" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18880,8 +18880,31 @@
       <c r="E805" t="n">
         <v>1.49500000476837</v>
       </c>
-      <c r="F805"/>
+      <c r="F805" t="n">
+        <v>1.50999999046326</v>
+      </c>
       <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C806" t="n">
+        <v>1.5349999666214</v>
+      </c>
+      <c r="D806" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E806" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F806"/>
+      <c r="G806" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18903,8 +18903,31 @@
       <c r="E806" t="n">
         <v>1.51999998092651</v>
       </c>
-      <c r="F806"/>
+      <c r="F806" t="n">
+        <v>1.48000001907349</v>
+      </c>
       <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C807" t="n">
+        <v>1.44500005245209</v>
+      </c>
+      <c r="D807" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E807" t="n">
+        <v>1.44500005245209</v>
+      </c>
+      <c r="F807"/>
+      <c r="G807" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18926,8 +18926,31 @@
       <c r="E807" t="n">
         <v>1.44500005245209</v>
       </c>
-      <c r="F807"/>
+      <c r="F807" t="n">
+        <v>1.39999997615814</v>
+      </c>
       <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C808" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="D808" t="n">
+        <v>1.38499999046326</v>
+      </c>
+      <c r="E808" t="n">
+        <v>1.41499996185303</v>
+      </c>
+      <c r="F808"/>
+      <c r="G808" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -18956,6 +18956,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B809" t="n">
+        <v>37500</v>
+      </c>
+      <c r="C809" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D809" t="n">
+        <v>1.31500005722046</v>
+      </c>
+      <c r="E809" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F809" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G809" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -21461,6 +21461,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B812" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C812" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D812" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E812" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F812" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G812" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="H812" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -21487,6 +21487,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B813" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C813" t="n">
+        <v>1.36500000953674</v>
+      </c>
+      <c r="D813" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E813" t="n">
+        <v>1.36500000953674</v>
+      </c>
+      <c r="F813" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="G813" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="H813" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -23955,6 +23955,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" t="s">
+        <v>9</v>
+      </c>
+      <c r="B814" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C814" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D814" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E814" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F814" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G814" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="H814" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I814" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="s">
+        <v>9</v>
+      </c>
+      <c r="B815" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C815" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="D815" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="E815" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F815" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G815" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H815" t="n">
+        <v>13500</v>
+      </c>
+      <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -24007,9 +24007,38 @@
         <v>1.29999995231628</v>
       </c>
       <c r="H815" t="n">
-        <v>13500</v>
+        <v>19500</v>
       </c>
       <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="s">
+        <v>9</v>
+      </c>
+      <c r="B816" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C816" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D816" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E816" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F816" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G816" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="H816" t="n">
+        <v>22500</v>
+      </c>
+      <c r="I816" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -24042,6 +24042,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="s">
+        <v>9</v>
+      </c>
+      <c r="B817" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C817" t="n">
+        <v>1.31500005722046</v>
+      </c>
+      <c r="D817" t="n">
+        <v>1.31500005722046</v>
+      </c>
+      <c r="E817" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="F817" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="G817" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="H817" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I817" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -24071,6 +24071,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="818">
+      <c r="A818" t="s">
+        <v>9</v>
+      </c>
+      <c r="B818" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C818" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D818" t="n">
+        <v>1.25499999523163</v>
+      </c>
+      <c r="E818" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F818" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G818" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H818" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I818" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -24100,6 +24100,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" t="s">
+        <v>9</v>
+      </c>
+      <c r="B819" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C819" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D819" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E819" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F819" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G819" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H819" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -24129,6 +24129,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" t="s">
+        <v>9</v>
+      </c>
+      <c r="B820" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C820" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D820" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E820" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F820" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G820" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H820" t="n">
+        <v>0</v>
+      </c>
+      <c r="I820" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="s">
+        <v>9</v>
+      </c>
+      <c r="B821" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C821" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D821" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E821" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F821" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G821" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H821" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I821" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -24187,6 +24187,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="s">
+        <v>9</v>
+      </c>
+      <c r="B822" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C822" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D822" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E822" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F822" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G822" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H822" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I822" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVN.MI.xlsx
+++ b/data/IVN.MI.xlsx
@@ -24216,6 +24216,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="823">
+      <c r="A823" t="s">
+        <v>9</v>
+      </c>
+      <c r="B823" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C823" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="D823" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="E823" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="F823" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="G823" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="H823" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I823" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
